--- a/data/trans_orig/P36B14-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B14-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de refrescos con azúcar en 2016</t>
+          <t>Población según la frecuencia de consumo de refrescos con azúcar en 2016 (tasa de respuesta: 99,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>335385</t>
+          <t>334915</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>386132</t>
+          <t>392116</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>504191</t>
+          <t>501182</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>567888</t>
+          <t>564541</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>850446</t>
+          <t>852636</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>933014</t>
+          <t>935854</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,09%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95311</t>
+          <t>95787</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>136592</t>
+          <t>134409</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>144577</t>
+          <t>143899</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>193033</t>
+          <t>191829</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>252893</t>
+          <t>251719</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>316775</t>
+          <t>315891</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>102031</t>
+          <t>101548</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>141029</t>
+          <t>142032</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>112959</t>
+          <t>111537</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>155250</t>
+          <t>154428</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>225486</t>
+          <t>223484</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>283357</t>
+          <t>284621</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68715</t>
+          <t>68442</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102279</t>
+          <t>102332</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76503</t>
+          <t>77993</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>113926</t>
+          <t>117065</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>155127</t>
+          <t>154699</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>205311</t>
+          <t>204182</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50013</t>
+          <t>49183</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79208</t>
+          <t>80371</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>44698</t>
+          <t>42748</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>75061</t>
+          <t>74694</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>101420</t>
+          <t>99801</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>144636</t>
+          <t>143885</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>477718</t>
+          <t>481434</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>562900</t>
+          <t>563134</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>539933</t>
+          <t>538095</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>621440</t>
+          <t>622440</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1041949</t>
+          <t>1046367</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1161029</t>
+          <t>1163360</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>279041</t>
+          <t>280553</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>347451</t>
+          <t>346067</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>266849</t>
+          <t>270694</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>332911</t>
+          <t>334212</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>570127</t>
+          <t>568963</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>666779</t>
+          <t>661697</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>358232</t>
+          <t>363019</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>431656</t>
+          <t>433586</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>335997</t>
+          <t>336391</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>406940</t>
+          <t>406596</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>717932</t>
+          <t>715869</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>815618</t>
+          <t>817392</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>408309</t>
+          <t>406022</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>483898</t>
+          <t>479606</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>343624</t>
+          <t>344521</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>416029</t>
+          <t>414618</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>766581</t>
+          <t>767542</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>873734</t>
+          <t>879068</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>356031</t>
+          <t>359600</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>430176</t>
+          <t>430376</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>313942</t>
+          <t>309785</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>379175</t>
+          <t>376653</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>690840</t>
+          <t>690088</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>786700</t>
+          <t>790476</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>159403</t>
+          <t>162747</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>206373</t>
+          <t>210614</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>160130</t>
+          <t>162137</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>209166</t>
+          <t>206116</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>336377</t>
+          <t>331339</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>400149</t>
+          <t>401375</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,76%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83389</t>
+          <t>84959</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>122406</t>
+          <t>122745</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>96828</t>
+          <t>98296</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>136427</t>
+          <t>136373</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>190835</t>
+          <t>191619</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>245921</t>
+          <t>246716</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>79293</t>
+          <t>78887</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>115195</t>
+          <t>114408</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>79312</t>
+          <t>78774</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>114966</t>
+          <t>114437</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>164251</t>
+          <t>168177</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>214234</t>
+          <t>221196</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>80512</t>
+          <t>81338</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>117117</t>
+          <t>117294</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>73104</t>
+          <t>72957</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>106773</t>
+          <t>106267</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>162990</t>
+          <t>160556</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>209711</t>
+          <t>211503</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52143</t>
+          <t>53186</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>82216</t>
+          <t>83153</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48527</t>
+          <t>50503</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>77997</t>
+          <t>78734</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>109154</t>
+          <t>110993</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>150587</t>
+          <t>152247</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1013826</t>
+          <t>1013776</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1118113</t>
+          <t>1120702</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1241941</t>
+          <t>1244891</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1355915</t>
+          <t>1356012</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2287932</t>
+          <t>2284799</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2453959</t>
+          <t>2437327</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,51%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>485963</t>
+          <t>488239</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>571669</t>
+          <t>572590</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>545003</t>
+          <t>542749</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>632280</t>
+          <t>632626</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1046432</t>
+          <t>1050359</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1173830</t>
+          <t>1172532</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>568149</t>
+          <t>567489</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>663321</t>
+          <t>660501</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>556324</t>
+          <t>555322</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>648502</t>
+          <t>645670</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1154019</t>
+          <t>1156665</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1278189</t>
+          <t>1275515</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>579903</t>
+          <t>583000</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>672733</t>
+          <t>670395</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>521024</t>
+          <t>518407</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>604308</t>
+          <t>607380</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1124261</t>
+          <t>1121944</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1251864</t>
+          <t>1240924</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>481083</t>
+          <t>484115</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>568845</t>
+          <t>566429</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>426521</t>
+          <t>428271</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>510181</t>
+          <t>506234</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>928999</t>
+          <t>922091</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1048020</t>
+          <t>1046183</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B14-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B14-Estudios-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>334915</t>
+          <t>333788</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>392116</t>
+          <t>388558</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>501182</t>
+          <t>496913</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>564541</t>
+          <t>563280</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>852636</t>
+          <t>850604</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>935854</t>
+          <t>937955</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,21%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95787</t>
+          <t>96391</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>134409</t>
+          <t>135479</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>143899</t>
+          <t>142807</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>191829</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
+          <t>14,5%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>19,4%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>282418</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>252748</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>316755</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>16,32%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>14,61%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>19,48%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>282418</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>251719</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>315891</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>16,32%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>14,55%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>101548</t>
+          <t>100291</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>142032</t>
+          <t>140886</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>111537</t>
+          <t>111870</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>154428</t>
+          <t>154095</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>223484</t>
+          <t>224008</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>284621</t>
+          <t>283841</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68442</t>
+          <t>66209</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102332</t>
+          <t>102296</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77993</t>
+          <t>77613</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>117065</t>
+          <t>117307</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>154699</t>
+          <t>153349</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>204182</t>
+          <t>202560</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49183</t>
+          <t>49390</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80371</t>
+          <t>81290</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42748</t>
+          <t>44136</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>74694</t>
+          <t>74211</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>99801</t>
+          <t>103295</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>143885</t>
+          <t>144810</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>481434</t>
+          <t>479744</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>563134</t>
+          <t>558475</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>538095</t>
+          <t>540361</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>622440</t>
+          <t>625266</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1046367</t>
+          <t>1041881</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1163360</t>
+          <t>1162924</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,77%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>280553</t>
+          <t>278384</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>346067</t>
+          <t>347064</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>270694</t>
+          <t>270855</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334212</t>
+          <t>334516</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>568963</t>
+          <t>571666</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>661697</t>
+          <t>663204</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>363019</t>
+          <t>361054</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>433586</t>
+          <t>436296</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>336391</t>
+          <t>336293</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>406596</t>
+          <t>405790</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>715869</t>
+          <t>720238</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>817392</t>
+          <t>818898</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>406022</t>
+          <t>405213</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>479606</t>
+          <t>482976</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>344521</t>
+          <t>342339</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>414618</t>
+          <t>410387</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>767542</t>
+          <t>774220</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>879068</t>
+          <t>872803</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>359600</t>
+          <t>358618</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>430376</t>
+          <t>429349</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>309785</t>
+          <t>315175</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>376653</t>
+          <t>380489</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>690088</t>
+          <t>690905</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>790476</t>
+          <t>787879</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>162747</t>
+          <t>162678</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>210614</t>
+          <t>207126</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>162137</t>
+          <t>159808</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>206116</t>
+          <t>207080</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>331339</t>
+          <t>335626</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>401375</t>
+          <t>398280</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,48%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>84959</t>
+          <t>82515</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>122745</t>
+          <t>119599</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>98296</t>
+          <t>97753</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>136373</t>
+          <t>138062</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>191619</t>
+          <t>192589</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>246716</t>
+          <t>248434</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,76%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>78887</t>
+          <t>78860</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>114408</t>
+          <t>116109</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>78774</t>
+          <t>77758</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>114437</t>
+          <t>114461</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>168177</t>
+          <t>167310</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>221196</t>
+          <t>218107</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>81338</t>
+          <t>79164</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>117294</t>
+          <t>115910</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>72957</t>
+          <t>73776</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>106267</t>
+          <t>107681</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>160556</t>
+          <t>160246</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>211503</t>
+          <t>212229</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53186</t>
+          <t>51873</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>83153</t>
+          <t>81888</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50503</t>
+          <t>49501</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>78734</t>
+          <t>77951</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>110993</t>
+          <t>111020</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>152247</t>
+          <t>150937</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1013776</t>
+          <t>1009435</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1120702</t>
+          <t>1121274</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1244891</t>
+          <t>1240995</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1356012</t>
+          <t>1364076</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2284799</t>
+          <t>2288300</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2437327</t>
+          <t>2445099</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,62%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>488239</t>
+          <t>486824</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>572590</t>
+          <t>573866</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>542749</t>
+          <t>538711</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>632626</t>
+          <t>632062</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1050359</t>
+          <t>1056728</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1172532</t>
+          <t>1179761</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>567489</t>
+          <t>559791</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>660501</t>
+          <t>656855</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>555322</t>
+          <t>554270</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>645670</t>
+          <t>647426</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1156665</t>
+          <t>1154120</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1275515</t>
+          <t>1277291</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>583000</t>
+          <t>580634</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>670395</t>
+          <t>670714</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>518407</t>
+          <t>516566</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>607380</t>
+          <t>607542</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1121944</t>
+          <t>1121656</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1240924</t>
+          <t>1246763</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>484115</t>
+          <t>483671</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>566429</t>
+          <t>571326</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>428271</t>
+          <t>430269</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>506234</t>
+          <t>509134</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>922091</t>
+          <t>931472</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1046183</t>
+          <t>1044254</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
